--- a/config/data/EnemyToughnessLayer.xlsx
+++ b/config/data/EnemyToughnessLayer.xlsx
@@ -1,127 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="EnemyToughnessLayer" sheetId="1" r:id="rId1"/>
+    <sheet name="EnemyToughnessLayer" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="30">
-  <si>
-    <t>@table</t>
-  </si>
-  <si>
-    <t>EnemyToughnessLayer</t>
-  </si>
-  <si>
-    <t>@mode</t>
-  </si>
-  <si>
-    <t>list</t>
-  </si>
-  <si>
-    <t>@key</t>
-  </si>
-  <si>
-    <t>@scope</t>
-  </si>
-  <si>
-    <t>all</t>
-  </si>
-  <si>
-    <t>@schema</t>
-  </si>
-  <si>
-    <t>579ceac0860c0986</t>
-  </si>
-  <si>
-    <t>#name</t>
-  </si>
-  <si>
-    <t>variant_id</t>
-  </si>
-  <si>
-    <t>sequence</t>
-  </si>
-  <si>
-    <t>layer_key</t>
-  </si>
-  <si>
-    <t>kind</t>
-  </si>
-  <si>
-    <t>maximum_decimal</t>
-  </si>
-  <si>
-    <t>recovery_ratio_decimal</t>
-  </si>
-  <si>
-    <t>active_at_start</t>
-  </si>
-  <si>
-    <t>#field</t>
-  </si>
-  <si>
-    <t>#type</t>
-  </si>
-  <si>
-    <t>ref&lt;EnemyVariant.id&gt;</t>
-  </si>
-  <si>
-    <t>i32</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>enum&lt;ToughnessLayerKind&gt;</t>
-  </si>
-  <si>
-    <t>bool</t>
-  </si>
-  <si>
-    <t>#scope</t>
-  </si>
-  <si>
-    <t>#input</t>
-  </si>
-  <si>
-    <t>range=1..16</t>
-  </si>
-  <si>
-    <t>length=1..120</t>
-  </si>
-  <si>
-    <t>length=1..32</t>
-  </si>
-  <si>
-    <t>#desc</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -140,13 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -434,163 +407,850 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>@table</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>EnemyToughnessLayer</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>@mode</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>@key</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>@scope</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>@schema</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>579ceac0860c0986</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>#name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>variant_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>sequence</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>layer_key</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>kind</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>maximum_decimal</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>recovery_ratio_decimal</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>active_at_start</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>#field</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>variant_id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>sequence</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>layer_key</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>kind</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>maximum_decimal</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>recovery_ratio_decimal</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>active_at_start</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>#type</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ref&lt;EnemyVariant.id&gt;</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>enum&lt;ToughnessLayerKind&gt;</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>#scope</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>#input</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>range=1..16</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>length=1..120</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>length=1..32</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>length=1..32</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>#desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>layer-1</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>101</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>layer-1</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>102</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>layer-1</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>103</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>layer-1</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>104</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>layer-1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>105</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>layer-1</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>105</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>layer-2</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sequential</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H14" t="b">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>105</v>
+      </c>
+      <c r="C15" t="n">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" t="s">
-        <v>6</v>
-      </c>
-      <c r="H5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>29</v>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>layer-3</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sequential</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>106</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>layer-1</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>107</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>layer-1</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>108</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>layer-1</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>109</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>layer-1</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>110</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>layer-1</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>111</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>layer-1</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>95</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>layer-1</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>96</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>layer-1</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>97</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>layer-1</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>98</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>layer-1</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>99</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>layer-1</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H26" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/config/data/EnemyToughnessLayer.xlsx
+++ b/config/data/EnemyToughnessLayer.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1253,6 +1253,37 @@
         <v>1</v>
       </c>
     </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>980001</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H27" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyToughnessLayer.xlsx
+++ b/config/data/EnemyToughnessLayer.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1284,6 +1284,37 @@
         <v>1</v>
       </c>
     </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>990001</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H28" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyToughnessLayer.xlsx
+++ b/config/data/EnemyToughnessLayer.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1315,6 +1315,37 @@
         <v>1</v>
       </c>
     </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H29" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyToughnessLayer.xlsx
+++ b/config/data/EnemyToughnessLayer.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1346,6 +1346,37 @@
         <v>1</v>
       </c>
     </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>1010001</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H30" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyToughnessLayer.xlsx
+++ b/config/data/EnemyToughnessLayer.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1377,6 +1377,37 @@
         <v>1</v>
       </c>
     </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>1020001</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H31" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyToughnessLayer.xlsx
+++ b/config/data/EnemyToughnessLayer.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1408,6 +1408,37 @@
         <v>1</v>
       </c>
     </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>1030001</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H32" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyToughnessLayer.xlsx
+++ b/config/data/EnemyToughnessLayer.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1439,6 +1439,37 @@
         <v>1</v>
       </c>
     </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>1040001</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H33" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyToughnessLayer.xlsx
+++ b/config/data/EnemyToughnessLayer.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1470,6 +1470,37 @@
         <v>1</v>
       </c>
     </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>1050001</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H34" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyToughnessLayer.xlsx
+++ b/config/data/EnemyToughnessLayer.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1501,6 +1501,37 @@
         <v>1</v>
       </c>
     </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>1060001</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H35" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyToughnessLayer.xlsx
+++ b/config/data/EnemyToughnessLayer.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1532,6 +1532,37 @@
         <v>1</v>
       </c>
     </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>1070001</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H36" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyToughnessLayer.xlsx
+++ b/config/data/EnemyToughnessLayer.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1563,6 +1563,37 @@
         <v>1</v>
       </c>
     </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>1080001</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H37" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyToughnessLayer.xlsx
+++ b/config/data/EnemyToughnessLayer.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1100,7 +1100,7 @@
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1131,7 +1131,7 @@
     </row>
     <row r="23">
       <c r="B23" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>540</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1162,7 +1162,7 @@
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1193,14 +1193,14 @@
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>layer-1</t>
+          <t>ordinary</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>420</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1224,14 +1224,14 @@
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>99</v>
+        <v>990001</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>layer-1</t>
+          <t>ordinary</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1255,7 +1255,7 @@
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>980001</v>
+        <v>1000001</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>480</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1286,7 +1286,7 @@
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>990001</v>
+        <v>1010001</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="29">
       <c r="B29" t="n">
-        <v>1000001</v>
+        <v>1020001</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>120</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1348,7 +1348,7 @@
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>1010001</v>
+        <v>1030001</v>
       </c>
       <c r="C30" t="n">
         <v>1</v>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>120</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1379,7 +1379,7 @@
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>1020001</v>
+        <v>1040001</v>
       </c>
       <c r="C31" t="n">
         <v>1</v>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1410,7 +1410,7 @@
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>1030001</v>
+        <v>1050001</v>
       </c>
       <c r="C32" t="n">
         <v>1</v>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1441,7 +1441,7 @@
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>1040001</v>
+        <v>1060001</v>
       </c>
       <c r="C33" t="n">
         <v>1</v>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>720</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1472,7 +1472,7 @@
     </row>
     <row r="34">
       <c r="B34" t="n">
-        <v>1050001</v>
+        <v>1070001</v>
       </c>
       <c r="C34" t="n">
         <v>1</v>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>450</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1503,7 +1503,7 @@
     </row>
     <row r="35">
       <c r="B35" t="n">
-        <v>1060001</v>
+        <v>1080001</v>
       </c>
       <c r="C35" t="n">
         <v>1</v>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>360</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1534,7 +1534,7 @@
     </row>
     <row r="36">
       <c r="B36" t="n">
-        <v>1070001</v>
+        <v>1090005</v>
       </c>
       <c r="C36" t="n">
         <v>1</v>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1565,7 +1565,7 @@
     </row>
     <row r="37">
       <c r="B37" t="n">
-        <v>1080001</v>
+        <v>1090006</v>
       </c>
       <c r="C37" t="n">
         <v>1</v>
@@ -1582,15 +1582,325 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>1090008</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H38" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>1090010</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H39" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>96</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H40" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>1090002</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t>360</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H37" t="b">
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H41" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>1090003</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H42" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>1090011</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H43" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>1090009</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H44" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>1090012</v>
+      </c>
+      <c r="C45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H45" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>1090004</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H46" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>95</v>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H47" t="b">
         <v>1</v>
       </c>
     </row>

--- a/config/data/EnemyToughnessLayer.xlsx
+++ b/config/data/EnemyToughnessLayer.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -666,7 +666,7 @@
     </row>
     <row r="8">
       <c r="B8" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
@@ -683,7 +683,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -697,7 +697,7 @@
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
@@ -714,7 +714,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -728,7 +728,7 @@
     </row>
     <row r="10">
       <c r="B10" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -759,7 +759,7 @@
     </row>
     <row r="11">
       <c r="B11" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C11" t="n">
         <v>1</v>
@@ -790,7 +790,7 @@
     </row>
     <row r="12">
       <c r="B12" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C12" t="n">
         <v>1</v>
@@ -807,7 +807,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>180</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -824,16 +824,16 @@
         <v>105</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>layer-1</t>
+          <t>layer-2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ordinary</t>
+          <t>Sequential</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="H13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -855,11 +855,11 @@
         <v>105</v>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>layer-2</t>
+          <t>layer-3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -883,24 +883,24 @@
     </row>
     <row r="15">
       <c r="B15" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>layer-3</t>
+          <t>layer-1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sequential</t>
+          <t>Ordinary</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -909,12 +909,12 @@
         </is>
       </c>
       <c r="H15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
@@ -945,7 +945,7 @@
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
@@ -962,7 +962,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -976,7 +976,7 @@
     </row>
     <row r="18">
       <c r="B18" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
@@ -1007,7 +1007,7 @@
     </row>
     <row r="19">
       <c r="B19" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C19" t="n">
         <v>1</v>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1038,7 +1038,7 @@
     </row>
     <row r="20">
       <c r="B20" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C20" t="n">
         <v>1</v>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1069,7 +1069,7 @@
     </row>
     <row r="21">
       <c r="B21" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C21" t="n">
         <v>1</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>540</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1100,14 +1100,14 @@
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>97</v>
+        <v>980001</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>layer-1</t>
+          <t>ordinary</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>420</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1131,14 +1131,14 @@
     </row>
     <row r="23">
       <c r="B23" t="n">
-        <v>98</v>
+        <v>990001</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>layer-1</t>
+          <t>ordinary</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1162,14 +1162,14 @@
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>99</v>
+        <v>1000001</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>layer-1</t>
+          <t>ordinary</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>480</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1193,7 +1193,7 @@
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>980001</v>
+        <v>1010001</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1224,7 +1224,7 @@
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>990001</v>
+        <v>1020001</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>120</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1255,7 +1255,7 @@
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>1000001</v>
+        <v>1030001</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>120</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1286,7 +1286,7 @@
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>1010001</v>
+        <v>1040001</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1317,7 +1317,7 @@
     </row>
     <row r="29">
       <c r="B29" t="n">
-        <v>1020001</v>
+        <v>1050001</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1348,7 +1348,7 @@
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>1030001</v>
+        <v>1060001</v>
       </c>
       <c r="C30" t="n">
         <v>1</v>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>720</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1379,7 +1379,7 @@
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>1040001</v>
+        <v>1070001</v>
       </c>
       <c r="C31" t="n">
         <v>1</v>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>450</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1410,7 +1410,7 @@
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>1050001</v>
+        <v>1080001</v>
       </c>
       <c r="C32" t="n">
         <v>1</v>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>360</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1441,7 +1441,7 @@
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>1060001</v>
+        <v>1090005</v>
       </c>
       <c r="C33" t="n">
         <v>1</v>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1472,7 +1472,7 @@
     </row>
     <row r="34">
       <c r="B34" t="n">
-        <v>1070001</v>
+        <v>1090006</v>
       </c>
       <c r="C34" t="n">
         <v>1</v>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1503,7 +1503,7 @@
     </row>
     <row r="35">
       <c r="B35" t="n">
-        <v>1080001</v>
+        <v>1090008</v>
       </c>
       <c r="C35" t="n">
         <v>1</v>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1534,7 +1534,7 @@
     </row>
     <row r="36">
       <c r="B36" t="n">
-        <v>1090005</v>
+        <v>1090010</v>
       </c>
       <c r="C36" t="n">
         <v>1</v>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1565,7 +1565,7 @@
     </row>
     <row r="37">
       <c r="B37" t="n">
-        <v>1090006</v>
+        <v>96</v>
       </c>
       <c r="C37" t="n">
         <v>1</v>
@@ -1596,7 +1596,7 @@
     </row>
     <row r="38">
       <c r="B38" t="n">
-        <v>1090008</v>
+        <v>1090002</v>
       </c>
       <c r="C38" t="n">
         <v>1</v>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>360</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1627,7 +1627,7 @@
     </row>
     <row r="39">
       <c r="B39" t="n">
-        <v>1090010</v>
+        <v>1090003</v>
       </c>
       <c r="C39" t="n">
         <v>1</v>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>360</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1658,7 +1658,7 @@
     </row>
     <row r="40">
       <c r="B40" t="n">
-        <v>96</v>
+        <v>1090011</v>
       </c>
       <c r="C40" t="n">
         <v>1</v>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>420</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1689,7 +1689,7 @@
     </row>
     <row r="41">
       <c r="B41" t="n">
-        <v>1090002</v>
+        <v>1090009</v>
       </c>
       <c r="C41" t="n">
         <v>1</v>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1720,7 +1720,7 @@
     </row>
     <row r="42">
       <c r="B42" t="n">
-        <v>1090003</v>
+        <v>1090012</v>
       </c>
       <c r="C42" t="n">
         <v>1</v>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1751,7 +1751,7 @@
     </row>
     <row r="43">
       <c r="B43" t="n">
-        <v>1090011</v>
+        <v>1090004</v>
       </c>
       <c r="C43" t="n">
         <v>1</v>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1782,7 +1782,7 @@
     </row>
     <row r="44">
       <c r="B44" t="n">
-        <v>1090009</v>
+        <v>95</v>
       </c>
       <c r="C44" t="n">
         <v>1</v>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1813,7 +1813,7 @@
     </row>
     <row r="45">
       <c r="B45" t="n">
-        <v>1090012</v>
+        <v>1100002</v>
       </c>
       <c r="C45" t="n">
         <v>1</v>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1844,7 +1844,7 @@
     </row>
     <row r="46">
       <c r="B46" t="n">
-        <v>1090004</v>
+        <v>1100011</v>
       </c>
       <c r="C46" t="n">
         <v>1</v>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -1875,7 +1875,7 @@
     </row>
     <row r="47">
       <c r="B47" t="n">
-        <v>95</v>
+        <v>1100004</v>
       </c>
       <c r="C47" t="n">
         <v>1</v>
@@ -1892,15 +1892,294 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H47" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="n">
+        <v>100</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H48" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>1100007</v>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H49" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="n">
+        <v>1100010</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H50" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>1100003</v>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="n">
+        <v>1100006</v>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H52" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="n">
+        <v>97</v>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H53" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>1100009</v>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H54" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>1100012</v>
+      </c>
+      <c r="C55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H47" t="b">
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H55" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="n">
+        <v>99</v>
+      </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H56" t="b">
         <v>1</v>
       </c>
     </row>

--- a/config/data/EnemyToughnessLayer.xlsx
+++ b/config/data/EnemyToughnessLayer.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J56"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -697,7 +697,7 @@
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
@@ -714,7 +714,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>180</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -728,24 +728,24 @@
     </row>
     <row r="10">
       <c r="B10" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>layer-1</t>
+          <t>layer-2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ordinary</t>
+          <t>Sequential</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>180</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -754,29 +754,29 @@
         </is>
       </c>
       <c r="H10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>layer-1</t>
+          <t>layer-3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ordinary</t>
+          <t>Sequential</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>180</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -785,12 +785,12 @@
         </is>
       </c>
       <c r="H11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C12" t="n">
         <v>1</v>
@@ -807,7 +807,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -821,24 +821,24 @@
     </row>
     <row r="13">
       <c r="B13" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>layer-2</t>
+          <t>layer-1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sequential</t>
+          <t>Ordinary</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -847,29 +847,29 @@
         </is>
       </c>
       <c r="H13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>layer-3</t>
+          <t>layer-1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sequential</t>
+          <t>Ordinary</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -878,12 +878,12 @@
         </is>
       </c>
       <c r="H14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C15" t="n">
         <v>1</v>
@@ -900,7 +900,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -914,7 +914,7 @@
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
@@ -945,7 +945,7 @@
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
@@ -962,7 +962,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -976,7 +976,7 @@
     </row>
     <row r="18">
       <c r="B18" t="n">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
@@ -993,7 +993,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>540</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1007,14 +1007,14 @@
     </row>
     <row r="19">
       <c r="B19" t="n">
-        <v>110</v>
+        <v>980001</v>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>layer-1</t>
+          <t>ordinary</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>420</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1038,14 +1038,14 @@
     </row>
     <row r="20">
       <c r="B20" t="n">
-        <v>111</v>
+        <v>990001</v>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>layer-1</t>
+          <t>ordinary</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1069,14 +1069,14 @@
     </row>
     <row r="21">
       <c r="B21" t="n">
-        <v>98</v>
+        <v>1000001</v>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>layer-1</t>
+          <t>ordinary</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>480</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1100,7 +1100,7 @@
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>980001</v>
+        <v>1010001</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1131,7 +1131,7 @@
     </row>
     <row r="23">
       <c r="B23" t="n">
-        <v>990001</v>
+        <v>1020001</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>120</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1162,7 +1162,7 @@
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>1000001</v>
+        <v>1030001</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>120</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1193,7 +1193,7 @@
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>1010001</v>
+        <v>1040001</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1224,7 +1224,7 @@
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>1020001</v>
+        <v>1050001</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1255,7 +1255,7 @@
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>1030001</v>
+        <v>1060001</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>720</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1286,7 +1286,7 @@
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>1040001</v>
+        <v>1070001</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>450</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1317,7 +1317,7 @@
     </row>
     <row r="29">
       <c r="B29" t="n">
-        <v>1050001</v>
+        <v>1080001</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>360</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1348,7 +1348,7 @@
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>1060001</v>
+        <v>1090005</v>
       </c>
       <c r="C30" t="n">
         <v>1</v>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1379,7 +1379,7 @@
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>1070001</v>
+        <v>1090006</v>
       </c>
       <c r="C31" t="n">
         <v>1</v>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1410,7 +1410,7 @@
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>1080001</v>
+        <v>1090008</v>
       </c>
       <c r="C32" t="n">
         <v>1</v>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1441,7 +1441,7 @@
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>1090005</v>
+        <v>1090010</v>
       </c>
       <c r="C33" t="n">
         <v>1</v>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1472,7 +1472,7 @@
     </row>
     <row r="34">
       <c r="B34" t="n">
-        <v>1090006</v>
+        <v>96</v>
       </c>
       <c r="C34" t="n">
         <v>1</v>
@@ -1503,7 +1503,7 @@
     </row>
     <row r="35">
       <c r="B35" t="n">
-        <v>1090008</v>
+        <v>1090002</v>
       </c>
       <c r="C35" t="n">
         <v>1</v>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>360</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1534,7 +1534,7 @@
     </row>
     <row r="36">
       <c r="B36" t="n">
-        <v>1090010</v>
+        <v>1090003</v>
       </c>
       <c r="C36" t="n">
         <v>1</v>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>360</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1565,7 +1565,7 @@
     </row>
     <row r="37">
       <c r="B37" t="n">
-        <v>96</v>
+        <v>1090011</v>
       </c>
       <c r="C37" t="n">
         <v>1</v>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>420</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1596,7 +1596,7 @@
     </row>
     <row r="38">
       <c r="B38" t="n">
-        <v>1090002</v>
+        <v>1090009</v>
       </c>
       <c r="C38" t="n">
         <v>1</v>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1627,7 +1627,7 @@
     </row>
     <row r="39">
       <c r="B39" t="n">
-        <v>1090003</v>
+        <v>1090012</v>
       </c>
       <c r="C39" t="n">
         <v>1</v>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1658,7 +1658,7 @@
     </row>
     <row r="40">
       <c r="B40" t="n">
-        <v>1090011</v>
+        <v>1090004</v>
       </c>
       <c r="C40" t="n">
         <v>1</v>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1689,7 +1689,7 @@
     </row>
     <row r="41">
       <c r="B41" t="n">
-        <v>1090009</v>
+        <v>95</v>
       </c>
       <c r="C41" t="n">
         <v>1</v>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1720,7 +1720,7 @@
     </row>
     <row r="42">
       <c r="B42" t="n">
-        <v>1090012</v>
+        <v>1100002</v>
       </c>
       <c r="C42" t="n">
         <v>1</v>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1751,7 +1751,7 @@
     </row>
     <row r="43">
       <c r="B43" t="n">
-        <v>1090004</v>
+        <v>1100011</v>
       </c>
       <c r="C43" t="n">
         <v>1</v>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1782,7 +1782,7 @@
     </row>
     <row r="44">
       <c r="B44" t="n">
-        <v>95</v>
+        <v>1100004</v>
       </c>
       <c r="C44" t="n">
         <v>1</v>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1813,7 +1813,7 @@
     </row>
     <row r="45">
       <c r="B45" t="n">
-        <v>1100002</v>
+        <v>100</v>
       </c>
       <c r="C45" t="n">
         <v>1</v>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>360</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1844,7 +1844,7 @@
     </row>
     <row r="46">
       <c r="B46" t="n">
-        <v>1100011</v>
+        <v>1100007</v>
       </c>
       <c r="C46" t="n">
         <v>1</v>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>360</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -1875,7 +1875,7 @@
     </row>
     <row r="47">
       <c r="B47" t="n">
-        <v>1100004</v>
+        <v>1100010</v>
       </c>
       <c r="C47" t="n">
         <v>1</v>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>480</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -1906,7 +1906,7 @@
     </row>
     <row r="48">
       <c r="B48" t="n">
-        <v>100</v>
+        <v>1100003</v>
       </c>
       <c r="C48" t="n">
         <v>1</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -1937,7 +1937,7 @@
     </row>
     <row r="49">
       <c r="B49" t="n">
-        <v>1100007</v>
+        <v>1100006</v>
       </c>
       <c r="C49" t="n">
         <v>1</v>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -1968,7 +1968,7 @@
     </row>
     <row r="50">
       <c r="B50" t="n">
-        <v>1100010</v>
+        <v>97</v>
       </c>
       <c r="C50" t="n">
         <v>1</v>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -1999,7 +1999,7 @@
     </row>
     <row r="51">
       <c r="B51" t="n">
-        <v>1100003</v>
+        <v>1100009</v>
       </c>
       <c r="C51" t="n">
         <v>1</v>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>720</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2030,7 +2030,7 @@
     </row>
     <row r="52">
       <c r="B52" t="n">
-        <v>1100006</v>
+        <v>1100012</v>
       </c>
       <c r="C52" t="n">
         <v>1</v>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2061,7 +2061,7 @@
     </row>
     <row r="53">
       <c r="B53" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C53" t="n">
         <v>1</v>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2092,7 +2092,7 @@
     </row>
     <row r="54">
       <c r="B54" t="n">
-        <v>1100009</v>
+        <v>103</v>
       </c>
       <c r="C54" t="n">
         <v>1</v>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2123,7 +2123,7 @@
     </row>
     <row r="55">
       <c r="B55" t="n">
-        <v>1100012</v>
+        <v>104</v>
       </c>
       <c r="C55" t="n">
         <v>1</v>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2154,7 +2154,7 @@
     </row>
     <row r="56">
       <c r="B56" t="n">
-        <v>99</v>
+        <v>1110002</v>
       </c>
       <c r="C56" t="n">
         <v>1</v>
@@ -2171,15 +2171,294 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H56" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="n">
+        <v>1110006</v>
+      </c>
+      <c r="C57" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H57" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="n">
+        <v>1110008</v>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H58" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="n">
+        <v>1110004</v>
+      </c>
+      <c r="C59" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H59" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="n">
+        <v>1110011</v>
+      </c>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H60" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="n">
+        <v>1110003</v>
+      </c>
+      <c r="C61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H61" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="n">
+        <v>102</v>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H62" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="n">
+        <v>1110009</v>
+      </c>
+      <c r="C63" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H63" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="n">
+        <v>1110001</v>
+      </c>
+      <c r="C64" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H56" t="b">
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H64" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="n">
+        <v>1110005</v>
+      </c>
+      <c r="C65" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H65" t="b">
         <v>1</v>
       </c>
     </row>

--- a/config/data/EnemyToughnessLayer.xlsx
+++ b/config/data/EnemyToughnessLayer.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:J74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,7 +790,7 @@
     </row>
     <row r="12">
       <c r="B12" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C12" t="n">
         <v>1</v>
@@ -807,7 +807,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -821,7 +821,7 @@
     </row>
     <row r="13">
       <c r="B13" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C13" t="n">
         <v>1</v>
@@ -852,7 +852,7 @@
     </row>
     <row r="14">
       <c r="B14" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C14" t="n">
         <v>1</v>
@@ -869,7 +869,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -883,7 +883,7 @@
     </row>
     <row r="15">
       <c r="B15" t="n">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="C15" t="n">
         <v>1</v>
@@ -900,7 +900,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>540</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -914,14 +914,14 @@
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>110</v>
+        <v>980001</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>layer-1</t>
+          <t>ordinary</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>420</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -945,14 +945,14 @@
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>111</v>
+        <v>990001</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>layer-1</t>
+          <t>ordinary</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -976,14 +976,14 @@
     </row>
     <row r="18">
       <c r="B18" t="n">
-        <v>98</v>
+        <v>1000001</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>layer-1</t>
+          <t>ordinary</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>480</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1007,7 +1007,7 @@
     </row>
     <row r="19">
       <c r="B19" t="n">
-        <v>980001</v>
+        <v>1010001</v>
       </c>
       <c r="C19" t="n">
         <v>1</v>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1038,7 +1038,7 @@
     </row>
     <row r="20">
       <c r="B20" t="n">
-        <v>990001</v>
+        <v>1020001</v>
       </c>
       <c r="C20" t="n">
         <v>1</v>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>120</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1069,7 +1069,7 @@
     </row>
     <row r="21">
       <c r="B21" t="n">
-        <v>1000001</v>
+        <v>1030001</v>
       </c>
       <c r="C21" t="n">
         <v>1</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>120</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1100,7 +1100,7 @@
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>1010001</v>
+        <v>1040001</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1131,7 +1131,7 @@
     </row>
     <row r="23">
       <c r="B23" t="n">
-        <v>1020001</v>
+        <v>1050001</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1162,7 +1162,7 @@
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>1030001</v>
+        <v>1060001</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>720</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1193,7 +1193,7 @@
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>1040001</v>
+        <v>1070001</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>450</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1224,7 +1224,7 @@
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>1050001</v>
+        <v>1080001</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>360</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1255,7 +1255,7 @@
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>1060001</v>
+        <v>1090005</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1286,7 +1286,7 @@
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>1070001</v>
+        <v>1090006</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1317,7 +1317,7 @@
     </row>
     <row r="29">
       <c r="B29" t="n">
-        <v>1080001</v>
+        <v>1090008</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1348,7 +1348,7 @@
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>1090005</v>
+        <v>1090010</v>
       </c>
       <c r="C30" t="n">
         <v>1</v>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1379,7 +1379,7 @@
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>1090006</v>
+        <v>96</v>
       </c>
       <c r="C31" t="n">
         <v>1</v>
@@ -1410,7 +1410,7 @@
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>1090008</v>
+        <v>1090002</v>
       </c>
       <c r="C32" t="n">
         <v>1</v>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>360</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1441,7 +1441,7 @@
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>1090010</v>
+        <v>1090003</v>
       </c>
       <c r="C33" t="n">
         <v>1</v>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>360</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1472,7 +1472,7 @@
     </row>
     <row r="34">
       <c r="B34" t="n">
-        <v>96</v>
+        <v>1090011</v>
       </c>
       <c r="C34" t="n">
         <v>1</v>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>420</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1503,7 +1503,7 @@
     </row>
     <row r="35">
       <c r="B35" t="n">
-        <v>1090002</v>
+        <v>1090009</v>
       </c>
       <c r="C35" t="n">
         <v>1</v>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1534,7 +1534,7 @@
     </row>
     <row r="36">
       <c r="B36" t="n">
-        <v>1090003</v>
+        <v>1090012</v>
       </c>
       <c r="C36" t="n">
         <v>1</v>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1565,7 +1565,7 @@
     </row>
     <row r="37">
       <c r="B37" t="n">
-        <v>1090011</v>
+        <v>1090004</v>
       </c>
       <c r="C37" t="n">
         <v>1</v>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1596,7 +1596,7 @@
     </row>
     <row r="38">
       <c r="B38" t="n">
-        <v>1090009</v>
+        <v>95</v>
       </c>
       <c r="C38" t="n">
         <v>1</v>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1627,7 +1627,7 @@
     </row>
     <row r="39">
       <c r="B39" t="n">
-        <v>1090012</v>
+        <v>1100002</v>
       </c>
       <c r="C39" t="n">
         <v>1</v>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1658,7 +1658,7 @@
     </row>
     <row r="40">
       <c r="B40" t="n">
-        <v>1090004</v>
+        <v>1100011</v>
       </c>
       <c r="C40" t="n">
         <v>1</v>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1689,7 +1689,7 @@
     </row>
     <row r="41">
       <c r="B41" t="n">
-        <v>95</v>
+        <v>1100004</v>
       </c>
       <c r="C41" t="n">
         <v>1</v>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1720,7 +1720,7 @@
     </row>
     <row r="42">
       <c r="B42" t="n">
-        <v>1100002</v>
+        <v>100</v>
       </c>
       <c r="C42" t="n">
         <v>1</v>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>360</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1751,7 +1751,7 @@
     </row>
     <row r="43">
       <c r="B43" t="n">
-        <v>1100011</v>
+        <v>1100007</v>
       </c>
       <c r="C43" t="n">
         <v>1</v>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>360</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1782,7 +1782,7 @@
     </row>
     <row r="44">
       <c r="B44" t="n">
-        <v>1100004</v>
+        <v>1100010</v>
       </c>
       <c r="C44" t="n">
         <v>1</v>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>480</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1813,7 +1813,7 @@
     </row>
     <row r="45">
       <c r="B45" t="n">
-        <v>100</v>
+        <v>1100003</v>
       </c>
       <c r="C45" t="n">
         <v>1</v>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1844,7 +1844,7 @@
     </row>
     <row r="46">
       <c r="B46" t="n">
-        <v>1100007</v>
+        <v>1100006</v>
       </c>
       <c r="C46" t="n">
         <v>1</v>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -1875,7 +1875,7 @@
     </row>
     <row r="47">
       <c r="B47" t="n">
-        <v>1100010</v>
+        <v>97</v>
       </c>
       <c r="C47" t="n">
         <v>1</v>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -1906,7 +1906,7 @@
     </row>
     <row r="48">
       <c r="B48" t="n">
-        <v>1100003</v>
+        <v>1100009</v>
       </c>
       <c r="C48" t="n">
         <v>1</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>720</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -1937,7 +1937,7 @@
     </row>
     <row r="49">
       <c r="B49" t="n">
-        <v>1100006</v>
+        <v>1100012</v>
       </c>
       <c r="C49" t="n">
         <v>1</v>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -1968,7 +1968,7 @@
     </row>
     <row r="50">
       <c r="B50" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C50" t="n">
         <v>1</v>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -1999,7 +1999,7 @@
     </row>
     <row r="51">
       <c r="B51" t="n">
-        <v>1100009</v>
+        <v>103</v>
       </c>
       <c r="C51" t="n">
         <v>1</v>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2030,7 +2030,7 @@
     </row>
     <row r="52">
       <c r="B52" t="n">
-        <v>1100012</v>
+        <v>104</v>
       </c>
       <c r="C52" t="n">
         <v>1</v>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2061,7 +2061,7 @@
     </row>
     <row r="53">
       <c r="B53" t="n">
-        <v>99</v>
+        <v>1110002</v>
       </c>
       <c r="C53" t="n">
         <v>1</v>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2092,7 +2092,7 @@
     </row>
     <row r="54">
       <c r="B54" t="n">
-        <v>103</v>
+        <v>1110006</v>
       </c>
       <c r="C54" t="n">
         <v>1</v>
@@ -2123,7 +2123,7 @@
     </row>
     <row r="55">
       <c r="B55" t="n">
-        <v>104</v>
+        <v>1110008</v>
       </c>
       <c r="C55" t="n">
         <v>1</v>
@@ -2154,7 +2154,7 @@
     </row>
     <row r="56">
       <c r="B56" t="n">
-        <v>1110002</v>
+        <v>1110004</v>
       </c>
       <c r="C56" t="n">
         <v>1</v>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2185,7 +2185,7 @@
     </row>
     <row r="57">
       <c r="B57" t="n">
-        <v>1110006</v>
+        <v>1110011</v>
       </c>
       <c r="C57" t="n">
         <v>1</v>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2216,7 +2216,7 @@
     </row>
     <row r="58">
       <c r="B58" t="n">
-        <v>1110008</v>
+        <v>1110003</v>
       </c>
       <c r="C58" t="n">
         <v>1</v>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>360</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2247,7 +2247,7 @@
     </row>
     <row r="59">
       <c r="B59" t="n">
-        <v>1110004</v>
+        <v>102</v>
       </c>
       <c r="C59" t="n">
         <v>1</v>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2278,7 +2278,7 @@
     </row>
     <row r="60">
       <c r="B60" t="n">
-        <v>1110011</v>
+        <v>1110009</v>
       </c>
       <c r="C60" t="n">
         <v>1</v>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2309,7 +2309,7 @@
     </row>
     <row r="61">
       <c r="B61" t="n">
-        <v>1110003</v>
+        <v>1110001</v>
       </c>
       <c r="C61" t="n">
         <v>1</v>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2340,7 +2340,7 @@
     </row>
     <row r="62">
       <c r="B62" t="n">
-        <v>102</v>
+        <v>1110005</v>
       </c>
       <c r="C62" t="n">
         <v>1</v>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2371,7 +2371,7 @@
     </row>
     <row r="63">
       <c r="B63" t="n">
-        <v>1110009</v>
+        <v>1120007</v>
       </c>
       <c r="C63" t="n">
         <v>1</v>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>120</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2402,7 +2402,7 @@
     </row>
     <row r="64">
       <c r="B64" t="n">
-        <v>1110001</v>
+        <v>1120010</v>
       </c>
       <c r="C64" t="n">
         <v>1</v>
@@ -2419,7 +2419,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2433,7 +2433,7 @@
     </row>
     <row r="65">
       <c r="B65" t="n">
-        <v>1110005</v>
+        <v>1120011</v>
       </c>
       <c r="C65" t="n">
         <v>1</v>
@@ -2450,15 +2450,294 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H65" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="n">
+        <v>1120003</v>
+      </c>
+      <c r="C66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H66" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="n">
+        <v>106</v>
+      </c>
+      <c r="C67" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H67" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="n">
+        <v>107</v>
+      </c>
+      <c r="C68" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H68" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="n">
+        <v>1120001</v>
+      </c>
+      <c r="C69" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H69" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="n">
+        <v>1120004</v>
+      </c>
+      <c r="C70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H70" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="n">
+        <v>1120012</v>
+      </c>
+      <c r="C71" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H71" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="n">
+        <v>108</v>
+      </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H65" t="b">
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H72" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="n">
+        <v>1120002</v>
+      </c>
+      <c r="C73" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H73" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="n">
+        <v>1120006</v>
+      </c>
+      <c r="C74" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H74" t="b">
         <v>1</v>
       </c>
     </row>

--- a/config/data/EnemyToughnessLayer.xlsx
+++ b/config/data/EnemyToughnessLayer.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J74"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2741,6 +2741,378 @@
         <v>1</v>
       </c>
     </row>
+    <row r="75">
+      <c r="B75" t="n">
+        <v>1130003</v>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H75" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="n">
+        <v>1130011</v>
+      </c>
+      <c r="C76" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H76" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="n">
+        <v>1130001</v>
+      </c>
+      <c r="C77" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H77" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="n">
+        <v>1130004</v>
+      </c>
+      <c r="C78" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H78" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="n">
+        <v>1130005</v>
+      </c>
+      <c r="C79" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H79" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="n">
+        <v>1130008</v>
+      </c>
+      <c r="C80" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H80" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="n">
+        <v>1130010</v>
+      </c>
+      <c r="C81" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H81" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="n">
+        <v>1130012</v>
+      </c>
+      <c r="C82" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H82" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="n">
+        <v>1130002</v>
+      </c>
+      <c r="C83" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H83" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="n">
+        <v>1130007</v>
+      </c>
+      <c r="C84" t="n">
+        <v>1</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H84" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="n">
+        <v>1130009</v>
+      </c>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H85" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="n">
+        <v>1130006</v>
+      </c>
+      <c r="C86" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H86" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EnemyToughnessLayer.xlsx
+++ b/config/data/EnemyToughnessLayer.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J86"/>
+  <dimension ref="A1:J97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -821,7 +821,7 @@
     </row>
     <row r="13">
       <c r="B13" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C13" t="n">
         <v>1</v>
@@ -838,7 +838,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -852,7 +852,7 @@
     </row>
     <row r="14">
       <c r="B14" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C14" t="n">
         <v>1</v>
@@ -869,7 +869,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>540</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -883,14 +883,14 @@
     </row>
     <row r="15">
       <c r="B15" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>layer-1</t>
+          <t>ordinary</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>420</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -914,7 +914,7 @@
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
@@ -931,7 +931,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -945,7 +945,7 @@
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>990001</v>
+        <v>1000001</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
@@ -962,7 +962,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>480</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -976,7 +976,7 @@
     </row>
     <row r="18">
       <c r="B18" t="n">
-        <v>1000001</v>
+        <v>1010001</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
@@ -993,7 +993,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1007,7 +1007,7 @@
     </row>
     <row r="19">
       <c r="B19" t="n">
-        <v>1010001</v>
+        <v>1020001</v>
       </c>
       <c r="C19" t="n">
         <v>1</v>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>120</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1038,7 +1038,7 @@
     </row>
     <row r="20">
       <c r="B20" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C20" t="n">
         <v>1</v>
@@ -1069,7 +1069,7 @@
     </row>
     <row r="21">
       <c r="B21" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C21" t="n">
         <v>1</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1100,7 +1100,7 @@
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>1040001</v>
+        <v>1050001</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1131,7 +1131,7 @@
     </row>
     <row r="23">
       <c r="B23" t="n">
-        <v>1050001</v>
+        <v>1060001</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>720</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1162,7 +1162,7 @@
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>450</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1193,7 +1193,7 @@
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>360</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1224,7 +1224,7 @@
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>1080001</v>
+        <v>1090005</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1255,7 +1255,7 @@
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>1090005</v>
+        <v>1090006</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1286,7 +1286,7 @@
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>1090006</v>
+        <v>1090008</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="29">
       <c r="B29" t="n">
-        <v>1090008</v>
+        <v>1090010</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
@@ -1348,7 +1348,7 @@
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>1090010</v>
+        <v>96</v>
       </c>
       <c r="C30" t="n">
         <v>1</v>
@@ -1379,7 +1379,7 @@
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>96</v>
+        <v>1090002</v>
       </c>
       <c r="C31" t="n">
         <v>1</v>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>360</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1410,7 +1410,7 @@
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>1090002</v>
+        <v>1090003</v>
       </c>
       <c r="C32" t="n">
         <v>1</v>
@@ -1441,7 +1441,7 @@
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>1090003</v>
+        <v>1090011</v>
       </c>
       <c r="C33" t="n">
         <v>1</v>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>420</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1472,7 +1472,7 @@
     </row>
     <row r="34">
       <c r="B34" t="n">
-        <v>1090011</v>
+        <v>1090009</v>
       </c>
       <c r="C34" t="n">
         <v>1</v>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1503,7 +1503,7 @@
     </row>
     <row r="35">
       <c r="B35" t="n">
-        <v>1090009</v>
+        <v>1090012</v>
       </c>
       <c r="C35" t="n">
         <v>1</v>
@@ -1534,7 +1534,7 @@
     </row>
     <row r="36">
       <c r="B36" t="n">
-        <v>1090012</v>
+        <v>1090004</v>
       </c>
       <c r="C36" t="n">
         <v>1</v>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1565,7 +1565,7 @@
     </row>
     <row r="37">
       <c r="B37" t="n">
-        <v>1090004</v>
+        <v>95</v>
       </c>
       <c r="C37" t="n">
         <v>1</v>
@@ -1596,7 +1596,7 @@
     </row>
     <row r="38">
       <c r="B38" t="n">
-        <v>95</v>
+        <v>1100002</v>
       </c>
       <c r="C38" t="n">
         <v>1</v>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1627,7 +1627,7 @@
     </row>
     <row r="39">
       <c r="B39" t="n">
-        <v>1100002</v>
+        <v>1100011</v>
       </c>
       <c r="C39" t="n">
         <v>1</v>
@@ -1658,7 +1658,7 @@
     </row>
     <row r="40">
       <c r="B40" t="n">
-        <v>1100011</v>
+        <v>1100004</v>
       </c>
       <c r="C40" t="n">
         <v>1</v>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1689,7 +1689,7 @@
     </row>
     <row r="41">
       <c r="B41" t="n">
-        <v>1100004</v>
+        <v>100</v>
       </c>
       <c r="C41" t="n">
         <v>1</v>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>360</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1720,7 +1720,7 @@
     </row>
     <row r="42">
       <c r="B42" t="n">
-        <v>100</v>
+        <v>1100007</v>
       </c>
       <c r="C42" t="n">
         <v>1</v>
@@ -1751,7 +1751,7 @@
     </row>
     <row r="43">
       <c r="B43" t="n">
-        <v>1100007</v>
+        <v>1100010</v>
       </c>
       <c r="C43" t="n">
         <v>1</v>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>480</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1782,7 +1782,7 @@
     </row>
     <row r="44">
       <c r="B44" t="n">
-        <v>1100010</v>
+        <v>1100003</v>
       </c>
       <c r="C44" t="n">
         <v>1</v>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1813,7 +1813,7 @@
     </row>
     <row r="45">
       <c r="B45" t="n">
-        <v>1100003</v>
+        <v>1100006</v>
       </c>
       <c r="C45" t="n">
         <v>1</v>
@@ -1844,7 +1844,7 @@
     </row>
     <row r="46">
       <c r="B46" t="n">
-        <v>1100006</v>
+        <v>97</v>
       </c>
       <c r="C46" t="n">
         <v>1</v>
@@ -1875,7 +1875,7 @@
     </row>
     <row r="47">
       <c r="B47" t="n">
-        <v>97</v>
+        <v>1100009</v>
       </c>
       <c r="C47" t="n">
         <v>1</v>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>720</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -1906,7 +1906,7 @@
     </row>
     <row r="48">
       <c r="B48" t="n">
-        <v>1100009</v>
+        <v>1100012</v>
       </c>
       <c r="C48" t="n">
         <v>1</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -1937,7 +1937,7 @@
     </row>
     <row r="49">
       <c r="B49" t="n">
-        <v>1100012</v>
+        <v>99</v>
       </c>
       <c r="C49" t="n">
         <v>1</v>
@@ -1968,7 +1968,7 @@
     </row>
     <row r="50">
       <c r="B50" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C50" t="n">
         <v>1</v>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -1999,7 +1999,7 @@
     </row>
     <row r="51">
       <c r="B51" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C51" t="n">
         <v>1</v>
@@ -2030,7 +2030,7 @@
     </row>
     <row r="52">
       <c r="B52" t="n">
-        <v>104</v>
+        <v>1110002</v>
       </c>
       <c r="C52" t="n">
         <v>1</v>
@@ -2061,7 +2061,7 @@
     </row>
     <row r="53">
       <c r="B53" t="n">
-        <v>1110002</v>
+        <v>1110006</v>
       </c>
       <c r="C53" t="n">
         <v>1</v>
@@ -2092,7 +2092,7 @@
     </row>
     <row r="54">
       <c r="B54" t="n">
-        <v>1110006</v>
+        <v>1110008</v>
       </c>
       <c r="C54" t="n">
         <v>1</v>
@@ -2123,7 +2123,7 @@
     </row>
     <row r="55">
       <c r="B55" t="n">
-        <v>1110008</v>
+        <v>1110004</v>
       </c>
       <c r="C55" t="n">
         <v>1</v>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2154,7 +2154,7 @@
     </row>
     <row r="56">
       <c r="B56" t="n">
-        <v>1110004</v>
+        <v>1110011</v>
       </c>
       <c r="C56" t="n">
         <v>1</v>
@@ -2185,7 +2185,7 @@
     </row>
     <row r="57">
       <c r="B57" t="n">
-        <v>1110011</v>
+        <v>1110003</v>
       </c>
       <c r="C57" t="n">
         <v>1</v>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>360</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2216,7 +2216,7 @@
     </row>
     <row r="58">
       <c r="B58" t="n">
-        <v>1110003</v>
+        <v>102</v>
       </c>
       <c r="C58" t="n">
         <v>1</v>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2247,7 +2247,7 @@
     </row>
     <row r="59">
       <c r="B59" t="n">
-        <v>102</v>
+        <v>1110009</v>
       </c>
       <c r="C59" t="n">
         <v>1</v>
@@ -2278,7 +2278,7 @@
     </row>
     <row r="60">
       <c r="B60" t="n">
-        <v>1110009</v>
+        <v>1110001</v>
       </c>
       <c r="C60" t="n">
         <v>1</v>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2309,7 +2309,7 @@
     </row>
     <row r="61">
       <c r="B61" t="n">
-        <v>1110001</v>
+        <v>1110005</v>
       </c>
       <c r="C61" t="n">
         <v>1</v>
@@ -2340,7 +2340,7 @@
     </row>
     <row r="62">
       <c r="B62" t="n">
-        <v>1110005</v>
+        <v>1120007</v>
       </c>
       <c r="C62" t="n">
         <v>1</v>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>120</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2371,7 +2371,7 @@
     </row>
     <row r="63">
       <c r="B63" t="n">
-        <v>1120007</v>
+        <v>1120010</v>
       </c>
       <c r="C63" t="n">
         <v>1</v>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2402,7 +2402,7 @@
     </row>
     <row r="64">
       <c r="B64" t="n">
-        <v>1120010</v>
+        <v>1120011</v>
       </c>
       <c r="C64" t="n">
         <v>1</v>
@@ -2433,7 +2433,7 @@
     </row>
     <row r="65">
       <c r="B65" t="n">
-        <v>1120011</v>
+        <v>1120003</v>
       </c>
       <c r="C65" t="n">
         <v>1</v>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2464,7 +2464,7 @@
     </row>
     <row r="66">
       <c r="B66" t="n">
-        <v>1120003</v>
+        <v>106</v>
       </c>
       <c r="C66" t="n">
         <v>1</v>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2495,7 +2495,7 @@
     </row>
     <row r="67">
       <c r="B67" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C67" t="n">
         <v>1</v>
@@ -2526,7 +2526,7 @@
     </row>
     <row r="68">
       <c r="B68" t="n">
-        <v>107</v>
+        <v>1120001</v>
       </c>
       <c r="C68" t="n">
         <v>1</v>
@@ -2557,7 +2557,7 @@
     </row>
     <row r="69">
       <c r="B69" t="n">
-        <v>1120001</v>
+        <v>1120004</v>
       </c>
       <c r="C69" t="n">
         <v>1</v>
@@ -2588,7 +2588,7 @@
     </row>
     <row r="70">
       <c r="B70" t="n">
-        <v>1120004</v>
+        <v>1120012</v>
       </c>
       <c r="C70" t="n">
         <v>1</v>
@@ -2619,7 +2619,7 @@
     </row>
     <row r="71">
       <c r="B71" t="n">
-        <v>1120012</v>
+        <v>108</v>
       </c>
       <c r="C71" t="n">
         <v>1</v>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2650,7 +2650,7 @@
     </row>
     <row r="72">
       <c r="B72" t="n">
-        <v>108</v>
+        <v>1120002</v>
       </c>
       <c r="C72" t="n">
         <v>1</v>
@@ -2681,7 +2681,7 @@
     </row>
     <row r="73">
       <c r="B73" t="n">
-        <v>1120002</v>
+        <v>1120006</v>
       </c>
       <c r="C73" t="n">
         <v>1</v>
@@ -2712,7 +2712,7 @@
     </row>
     <row r="74">
       <c r="B74" t="n">
-        <v>1120006</v>
+        <v>1130003</v>
       </c>
       <c r="C74" t="n">
         <v>1</v>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -2743,7 +2743,7 @@
     </row>
     <row r="75">
       <c r="B75" t="n">
-        <v>1130003</v>
+        <v>1130011</v>
       </c>
       <c r="C75" t="n">
         <v>1</v>
@@ -2774,7 +2774,7 @@
     </row>
     <row r="76">
       <c r="B76" t="n">
-        <v>1130011</v>
+        <v>1130001</v>
       </c>
       <c r="C76" t="n">
         <v>1</v>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>360</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2805,7 +2805,7 @@
     </row>
     <row r="77">
       <c r="B77" t="n">
-        <v>1130001</v>
+        <v>1130004</v>
       </c>
       <c r="C77" t="n">
         <v>1</v>
@@ -2836,7 +2836,7 @@
     </row>
     <row r="78">
       <c r="B78" t="n">
-        <v>1130004</v>
+        <v>1130005</v>
       </c>
       <c r="C78" t="n">
         <v>1</v>
@@ -2867,7 +2867,7 @@
     </row>
     <row r="79">
       <c r="B79" t="n">
-        <v>1130005</v>
+        <v>1130008</v>
       </c>
       <c r="C79" t="n">
         <v>1</v>
@@ -2898,7 +2898,7 @@
     </row>
     <row r="80">
       <c r="B80" t="n">
-        <v>1130008</v>
+        <v>1130010</v>
       </c>
       <c r="C80" t="n">
         <v>1</v>
@@ -2929,7 +2929,7 @@
     </row>
     <row r="81">
       <c r="B81" t="n">
-        <v>1130010</v>
+        <v>1130012</v>
       </c>
       <c r="C81" t="n">
         <v>1</v>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>420</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -2960,7 +2960,7 @@
     </row>
     <row r="82">
       <c r="B82" t="n">
-        <v>1130012</v>
+        <v>1130002</v>
       </c>
       <c r="C82" t="n">
         <v>1</v>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -2991,7 +2991,7 @@
     </row>
     <row r="83">
       <c r="B83" t="n">
-        <v>1130002</v>
+        <v>1130007</v>
       </c>
       <c r="C83" t="n">
         <v>1</v>
@@ -3022,7 +3022,7 @@
     </row>
     <row r="84">
       <c r="B84" t="n">
-        <v>1130007</v>
+        <v>1130009</v>
       </c>
       <c r="C84" t="n">
         <v>1</v>
@@ -3053,7 +3053,7 @@
     </row>
     <row r="85">
       <c r="B85" t="n">
-        <v>1130009</v>
+        <v>1130006</v>
       </c>
       <c r="C85" t="n">
         <v>1</v>
@@ -3070,7 +3070,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3084,7 +3084,7 @@
     </row>
     <row r="86">
       <c r="B86" t="n">
-        <v>1130006</v>
+        <v>1140001</v>
       </c>
       <c r="C86" t="n">
         <v>1</v>
@@ -3101,15 +3101,356 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H86" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="n">
+        <v>1140006</v>
+      </c>
+      <c r="C87" t="n">
+        <v>1</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H87" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="n">
+        <v>1140007</v>
+      </c>
+      <c r="C88" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H88" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="n">
+        <v>1140012</v>
+      </c>
+      <c r="C89" t="n">
+        <v>1</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H89" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="n">
+        <v>110</v>
+      </c>
+      <c r="C90" t="n">
+        <v>1</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H90" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="n">
+        <v>1140008</v>
+      </c>
+      <c r="C91" t="n">
+        <v>1</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H91" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="n">
+        <v>1140009</v>
+      </c>
+      <c r="C92" t="n">
+        <v>1</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H92" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="n">
+        <v>1140002</v>
+      </c>
+      <c r="C93" t="n">
+        <v>1</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H86" t="b">
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H93" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="n">
+        <v>1140003</v>
+      </c>
+      <c r="C94" t="n">
+        <v>1</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H94" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="n">
+        <v>1140004</v>
+      </c>
+      <c r="C95" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H95" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="n">
+        <v>1140005</v>
+      </c>
+      <c r="C96" t="n">
+        <v>1</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H96" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="n">
+        <v>1140010</v>
+      </c>
+      <c r="C97" t="n">
+        <v>1</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H97" t="b">
         <v>1</v>
       </c>
     </row>

--- a/config/data/EnemyToughnessLayer.xlsx
+++ b/config/data/EnemyToughnessLayer.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J97"/>
+  <dimension ref="A1:J99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -821,7 +821,7 @@
     </row>
     <row r="13">
       <c r="B13" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C13" t="n">
         <v>1</v>
@@ -838,7 +838,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>540</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -852,14 +852,14 @@
     </row>
     <row r="14">
       <c r="B14" t="n">
-        <v>98</v>
+        <v>980001</v>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>layer-1</t>
+          <t>ordinary</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>420</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -883,7 +883,7 @@
     </row>
     <row r="15">
       <c r="B15" t="n">
-        <v>980001</v>
+        <v>990001</v>
       </c>
       <c r="C15" t="n">
         <v>1</v>
@@ -900,7 +900,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -914,7 +914,7 @@
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>990001</v>
+        <v>1000001</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
@@ -931,7 +931,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>480</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -945,7 +945,7 @@
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>1000001</v>
+        <v>1010001</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
@@ -962,7 +962,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -976,7 +976,7 @@
     </row>
     <row r="18">
       <c r="B18" t="n">
-        <v>1010001</v>
+        <v>1020001</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
@@ -993,7 +993,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>120</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1007,7 +1007,7 @@
     </row>
     <row r="19">
       <c r="B19" t="n">
-        <v>1020001</v>
+        <v>1030001</v>
       </c>
       <c r="C19" t="n">
         <v>1</v>
@@ -1038,7 +1038,7 @@
     </row>
     <row r="20">
       <c r="B20" t="n">
-        <v>1030001</v>
+        <v>1040001</v>
       </c>
       <c r="C20" t="n">
         <v>1</v>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1069,7 +1069,7 @@
     </row>
     <row r="21">
       <c r="B21" t="n">
-        <v>1040001</v>
+        <v>1050001</v>
       </c>
       <c r="C21" t="n">
         <v>1</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1100,7 +1100,7 @@
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>1050001</v>
+        <v>1060001</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>720</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1131,7 +1131,7 @@
     </row>
     <row r="23">
       <c r="B23" t="n">
-        <v>1060001</v>
+        <v>1070001</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>450</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1162,7 +1162,7 @@
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>1070001</v>
+        <v>1080001</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>360</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1193,7 +1193,7 @@
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>1080001</v>
+        <v>1090005</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1224,7 +1224,7 @@
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>1090005</v>
+        <v>1090006</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1255,7 +1255,7 @@
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>1090006</v>
+        <v>1090008</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
@@ -1286,7 +1286,7 @@
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>1090008</v>
+        <v>1090010</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="29">
       <c r="B29" t="n">
-        <v>1090010</v>
+        <v>96</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
@@ -1348,7 +1348,7 @@
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>96</v>
+        <v>1090002</v>
       </c>
       <c r="C30" t="n">
         <v>1</v>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>360</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1379,7 +1379,7 @@
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>1090002</v>
+        <v>1090003</v>
       </c>
       <c r="C31" t="n">
         <v>1</v>
@@ -1410,7 +1410,7 @@
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>1090003</v>
+        <v>1090011</v>
       </c>
       <c r="C32" t="n">
         <v>1</v>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>420</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1441,7 +1441,7 @@
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>1090011</v>
+        <v>1090009</v>
       </c>
       <c r="C33" t="n">
         <v>1</v>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1472,7 +1472,7 @@
     </row>
     <row r="34">
       <c r="B34" t="n">
-        <v>1090009</v>
+        <v>1090012</v>
       </c>
       <c r="C34" t="n">
         <v>1</v>
@@ -1503,7 +1503,7 @@
     </row>
     <row r="35">
       <c r="B35" t="n">
-        <v>1090012</v>
+        <v>1090004</v>
       </c>
       <c r="C35" t="n">
         <v>1</v>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1534,7 +1534,7 @@
     </row>
     <row r="36">
       <c r="B36" t="n">
-        <v>1090004</v>
+        <v>95</v>
       </c>
       <c r="C36" t="n">
         <v>1</v>
@@ -1565,7 +1565,7 @@
     </row>
     <row r="37">
       <c r="B37" t="n">
-        <v>95</v>
+        <v>1100002</v>
       </c>
       <c r="C37" t="n">
         <v>1</v>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1596,7 +1596,7 @@
     </row>
     <row r="38">
       <c r="B38" t="n">
-        <v>1100002</v>
+        <v>1100011</v>
       </c>
       <c r="C38" t="n">
         <v>1</v>
@@ -1627,7 +1627,7 @@
     </row>
     <row r="39">
       <c r="B39" t="n">
-        <v>1100011</v>
+        <v>1100004</v>
       </c>
       <c r="C39" t="n">
         <v>1</v>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1658,7 +1658,7 @@
     </row>
     <row r="40">
       <c r="B40" t="n">
-        <v>1100004</v>
+        <v>100</v>
       </c>
       <c r="C40" t="n">
         <v>1</v>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>360</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1689,7 +1689,7 @@
     </row>
     <row r="41">
       <c r="B41" t="n">
-        <v>100</v>
+        <v>1100007</v>
       </c>
       <c r="C41" t="n">
         <v>1</v>
@@ -1720,7 +1720,7 @@
     </row>
     <row r="42">
       <c r="B42" t="n">
-        <v>1100007</v>
+        <v>1100010</v>
       </c>
       <c r="C42" t="n">
         <v>1</v>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>480</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1751,7 +1751,7 @@
     </row>
     <row r="43">
       <c r="B43" t="n">
-        <v>1100010</v>
+        <v>1100003</v>
       </c>
       <c r="C43" t="n">
         <v>1</v>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1782,7 +1782,7 @@
     </row>
     <row r="44">
       <c r="B44" t="n">
-        <v>1100003</v>
+        <v>1100006</v>
       </c>
       <c r="C44" t="n">
         <v>1</v>
@@ -1813,7 +1813,7 @@
     </row>
     <row r="45">
       <c r="B45" t="n">
-        <v>1100006</v>
+        <v>97</v>
       </c>
       <c r="C45" t="n">
         <v>1</v>
@@ -1844,7 +1844,7 @@
     </row>
     <row r="46">
       <c r="B46" t="n">
-        <v>97</v>
+        <v>1100009</v>
       </c>
       <c r="C46" t="n">
         <v>1</v>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>720</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -1875,7 +1875,7 @@
     </row>
     <row r="47">
       <c r="B47" t="n">
-        <v>1100009</v>
+        <v>1100012</v>
       </c>
       <c r="C47" t="n">
         <v>1</v>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -1906,7 +1906,7 @@
     </row>
     <row r="48">
       <c r="B48" t="n">
-        <v>1100012</v>
+        <v>99</v>
       </c>
       <c r="C48" t="n">
         <v>1</v>
@@ -1937,7 +1937,7 @@
     </row>
     <row r="49">
       <c r="B49" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C49" t="n">
         <v>1</v>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -1968,7 +1968,7 @@
     </row>
     <row r="50">
       <c r="B50" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C50" t="n">
         <v>1</v>
@@ -1999,7 +1999,7 @@
     </row>
     <row r="51">
       <c r="B51" t="n">
-        <v>104</v>
+        <v>1110002</v>
       </c>
       <c r="C51" t="n">
         <v>1</v>
@@ -2030,7 +2030,7 @@
     </row>
     <row r="52">
       <c r="B52" t="n">
-        <v>1110002</v>
+        <v>1110006</v>
       </c>
       <c r="C52" t="n">
         <v>1</v>
@@ -2061,7 +2061,7 @@
     </row>
     <row r="53">
       <c r="B53" t="n">
-        <v>1110006</v>
+        <v>1110008</v>
       </c>
       <c r="C53" t="n">
         <v>1</v>
@@ -2092,7 +2092,7 @@
     </row>
     <row r="54">
       <c r="B54" t="n">
-        <v>1110008</v>
+        <v>1110004</v>
       </c>
       <c r="C54" t="n">
         <v>1</v>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2123,7 +2123,7 @@
     </row>
     <row r="55">
       <c r="B55" t="n">
-        <v>1110004</v>
+        <v>1110011</v>
       </c>
       <c r="C55" t="n">
         <v>1</v>
@@ -2154,7 +2154,7 @@
     </row>
     <row r="56">
       <c r="B56" t="n">
-        <v>1110011</v>
+        <v>1110003</v>
       </c>
       <c r="C56" t="n">
         <v>1</v>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>360</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2185,7 +2185,7 @@
     </row>
     <row r="57">
       <c r="B57" t="n">
-        <v>1110003</v>
+        <v>102</v>
       </c>
       <c r="C57" t="n">
         <v>1</v>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2216,7 +2216,7 @@
     </row>
     <row r="58">
       <c r="B58" t="n">
-        <v>102</v>
+        <v>1110009</v>
       </c>
       <c r="C58" t="n">
         <v>1</v>
@@ -2247,7 +2247,7 @@
     </row>
     <row r="59">
       <c r="B59" t="n">
-        <v>1110009</v>
+        <v>1110001</v>
       </c>
       <c r="C59" t="n">
         <v>1</v>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2278,7 +2278,7 @@
     </row>
     <row r="60">
       <c r="B60" t="n">
-        <v>1110001</v>
+        <v>1110005</v>
       </c>
       <c r="C60" t="n">
         <v>1</v>
@@ -2309,7 +2309,7 @@
     </row>
     <row r="61">
       <c r="B61" t="n">
-        <v>1110005</v>
+        <v>1120007</v>
       </c>
       <c r="C61" t="n">
         <v>1</v>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>120</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2340,7 +2340,7 @@
     </row>
     <row r="62">
       <c r="B62" t="n">
-        <v>1120007</v>
+        <v>1120010</v>
       </c>
       <c r="C62" t="n">
         <v>1</v>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2371,7 +2371,7 @@
     </row>
     <row r="63">
       <c r="B63" t="n">
-        <v>1120010</v>
+        <v>1120011</v>
       </c>
       <c r="C63" t="n">
         <v>1</v>
@@ -2402,7 +2402,7 @@
     </row>
     <row r="64">
       <c r="B64" t="n">
-        <v>1120011</v>
+        <v>1120003</v>
       </c>
       <c r="C64" t="n">
         <v>1</v>
@@ -2419,7 +2419,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2433,7 +2433,7 @@
     </row>
     <row r="65">
       <c r="B65" t="n">
-        <v>1120003</v>
+        <v>106</v>
       </c>
       <c r="C65" t="n">
         <v>1</v>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2464,7 +2464,7 @@
     </row>
     <row r="66">
       <c r="B66" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C66" t="n">
         <v>1</v>
@@ -2495,7 +2495,7 @@
     </row>
     <row r="67">
       <c r="B67" t="n">
-        <v>107</v>
+        <v>1120001</v>
       </c>
       <c r="C67" t="n">
         <v>1</v>
@@ -2526,7 +2526,7 @@
     </row>
     <row r="68">
       <c r="B68" t="n">
-        <v>1120001</v>
+        <v>1120004</v>
       </c>
       <c r="C68" t="n">
         <v>1</v>
@@ -2557,7 +2557,7 @@
     </row>
     <row r="69">
       <c r="B69" t="n">
-        <v>1120004</v>
+        <v>1120012</v>
       </c>
       <c r="C69" t="n">
         <v>1</v>
@@ -2588,7 +2588,7 @@
     </row>
     <row r="70">
       <c r="B70" t="n">
-        <v>1120012</v>
+        <v>108</v>
       </c>
       <c r="C70" t="n">
         <v>1</v>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2619,7 +2619,7 @@
     </row>
     <row r="71">
       <c r="B71" t="n">
-        <v>108</v>
+        <v>1120002</v>
       </c>
       <c r="C71" t="n">
         <v>1</v>
@@ -2650,7 +2650,7 @@
     </row>
     <row r="72">
       <c r="B72" t="n">
-        <v>1120002</v>
+        <v>1120006</v>
       </c>
       <c r="C72" t="n">
         <v>1</v>
@@ -2681,7 +2681,7 @@
     </row>
     <row r="73">
       <c r="B73" t="n">
-        <v>1120006</v>
+        <v>1130003</v>
       </c>
       <c r="C73" t="n">
         <v>1</v>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2712,7 +2712,7 @@
     </row>
     <row r="74">
       <c r="B74" t="n">
-        <v>1130003</v>
+        <v>1130011</v>
       </c>
       <c r="C74" t="n">
         <v>1</v>
@@ -2743,7 +2743,7 @@
     </row>
     <row r="75">
       <c r="B75" t="n">
-        <v>1130011</v>
+        <v>1130001</v>
       </c>
       <c r="C75" t="n">
         <v>1</v>
@@ -2760,7 +2760,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>360</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2774,7 +2774,7 @@
     </row>
     <row r="76">
       <c r="B76" t="n">
-        <v>1130001</v>
+        <v>1130004</v>
       </c>
       <c r="C76" t="n">
         <v>1</v>
@@ -2805,7 +2805,7 @@
     </row>
     <row r="77">
       <c r="B77" t="n">
-        <v>1130004</v>
+        <v>1130005</v>
       </c>
       <c r="C77" t="n">
         <v>1</v>
@@ -2836,7 +2836,7 @@
     </row>
     <row r="78">
       <c r="B78" t="n">
-        <v>1130005</v>
+        <v>1130008</v>
       </c>
       <c r="C78" t="n">
         <v>1</v>
@@ -2867,7 +2867,7 @@
     </row>
     <row r="79">
       <c r="B79" t="n">
-        <v>1130008</v>
+        <v>1130010</v>
       </c>
       <c r="C79" t="n">
         <v>1</v>
@@ -2898,7 +2898,7 @@
     </row>
     <row r="80">
       <c r="B80" t="n">
-        <v>1130010</v>
+        <v>1130012</v>
       </c>
       <c r="C80" t="n">
         <v>1</v>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>420</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -2929,7 +2929,7 @@
     </row>
     <row r="81">
       <c r="B81" t="n">
-        <v>1130012</v>
+        <v>1130002</v>
       </c>
       <c r="C81" t="n">
         <v>1</v>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -2960,7 +2960,7 @@
     </row>
     <row r="82">
       <c r="B82" t="n">
-        <v>1130002</v>
+        <v>1130007</v>
       </c>
       <c r="C82" t="n">
         <v>1</v>
@@ -2991,7 +2991,7 @@
     </row>
     <row r="83">
       <c r="B83" t="n">
-        <v>1130007</v>
+        <v>1130009</v>
       </c>
       <c r="C83" t="n">
         <v>1</v>
@@ -3022,7 +3022,7 @@
     </row>
     <row r="84">
       <c r="B84" t="n">
-        <v>1130009</v>
+        <v>1130006</v>
       </c>
       <c r="C84" t="n">
         <v>1</v>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3053,7 +3053,7 @@
     </row>
     <row r="85">
       <c r="B85" t="n">
-        <v>1130006</v>
+        <v>1140001</v>
       </c>
       <c r="C85" t="n">
         <v>1</v>
@@ -3070,7 +3070,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3084,7 +3084,7 @@
     </row>
     <row r="86">
       <c r="B86" t="n">
-        <v>1140001</v>
+        <v>1140006</v>
       </c>
       <c r="C86" t="n">
         <v>1</v>
@@ -3115,7 +3115,7 @@
     </row>
     <row r="87">
       <c r="B87" t="n">
-        <v>1140006</v>
+        <v>1140007</v>
       </c>
       <c r="C87" t="n">
         <v>1</v>
@@ -3146,7 +3146,7 @@
     </row>
     <row r="88">
       <c r="B88" t="n">
-        <v>1140007</v>
+        <v>1140012</v>
       </c>
       <c r="C88" t="n">
         <v>1</v>
@@ -3163,7 +3163,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>420</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3177,7 +3177,7 @@
     </row>
     <row r="89">
       <c r="B89" t="n">
-        <v>1140012</v>
+        <v>110</v>
       </c>
       <c r="C89" t="n">
         <v>1</v>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3208,7 +3208,7 @@
     </row>
     <row r="90">
       <c r="B90" t="n">
-        <v>110</v>
+        <v>1140008</v>
       </c>
       <c r="C90" t="n">
         <v>1</v>
@@ -3239,7 +3239,7 @@
     </row>
     <row r="91">
       <c r="B91" t="n">
-        <v>1140008</v>
+        <v>1140009</v>
       </c>
       <c r="C91" t="n">
         <v>1</v>
@@ -3270,7 +3270,7 @@
     </row>
     <row r="92">
       <c r="B92" t="n">
-        <v>1140009</v>
+        <v>1140002</v>
       </c>
       <c r="C92" t="n">
         <v>1</v>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3301,7 +3301,7 @@
     </row>
     <row r="93">
       <c r="B93" t="n">
-        <v>1140002</v>
+        <v>1140003</v>
       </c>
       <c r="C93" t="n">
         <v>1</v>
@@ -3332,7 +3332,7 @@
     </row>
     <row r="94">
       <c r="B94" t="n">
-        <v>1140003</v>
+        <v>1140004</v>
       </c>
       <c r="C94" t="n">
         <v>1</v>
@@ -3363,7 +3363,7 @@
     </row>
     <row r="95">
       <c r="B95" t="n">
-        <v>1140004</v>
+        <v>1140005</v>
       </c>
       <c r="C95" t="n">
         <v>1</v>
@@ -3394,7 +3394,7 @@
     </row>
     <row r="96">
       <c r="B96" t="n">
-        <v>1140005</v>
+        <v>1140010</v>
       </c>
       <c r="C96" t="n">
         <v>1</v>
@@ -3425,7 +3425,7 @@
     </row>
     <row r="97">
       <c r="B97" t="n">
-        <v>1140010</v>
+        <v>1150002</v>
       </c>
       <c r="C97" t="n">
         <v>1</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3451,6 +3451,68 @@
         </is>
       </c>
       <c r="H97" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="n">
+        <v>111</v>
+      </c>
+      <c r="C98" t="n">
+        <v>1</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H98" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="n">
+        <v>1150003</v>
+      </c>
+      <c r="C99" t="n">
+        <v>1</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H99" t="b">
         <v>1</v>
       </c>
     </row>

--- a/config/data/EnemyToughnessLayer.xlsx
+++ b/config/data/EnemyToughnessLayer.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -666,7 +666,7 @@
     </row>
     <row r="8">
       <c r="B8" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
@@ -683,7 +683,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -697,7 +697,7 @@
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
@@ -714,7 +714,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>180</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -728,24 +728,24 @@
     </row>
     <row r="10">
       <c r="B10" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>layer-1</t>
+          <t>layer-2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ordinary</t>
+          <t>Sequential</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>180</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -754,29 +754,29 @@
         </is>
       </c>
       <c r="H10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>layer-1</t>
+          <t>layer-3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ordinary</t>
+          <t>Sequential</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>180</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -785,12 +785,12 @@
         </is>
       </c>
       <c r="H11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C12" t="n">
         <v>1</v>
@@ -807,7 +807,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -821,7 +821,7 @@
     </row>
     <row r="13">
       <c r="B13" t="n">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C13" t="n">
         <v>1</v>
@@ -838,7 +838,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>540</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -852,24 +852,24 @@
     </row>
     <row r="14">
       <c r="B14" t="n">
-        <v>105</v>
+        <v>980001</v>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>layer-2</t>
+          <t>ordinary</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sequential</t>
+          <t>Ordinary</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>420</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -878,29 +878,29 @@
         </is>
       </c>
       <c r="H14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="n">
-        <v>105</v>
+        <v>990001</v>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>layer-3</t>
+          <t>ordinary</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sequential</t>
+          <t>Ordinary</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -909,19 +909,19 @@
         </is>
       </c>
       <c r="H15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>106</v>
+        <v>1000001</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>layer-1</t>
+          <t>ordinary</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>480</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -945,14 +945,14 @@
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>107</v>
+        <v>1010001</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>layer-1</t>
+          <t>ordinary</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -976,14 +976,14 @@
     </row>
     <row r="18">
       <c r="B18" t="n">
-        <v>108</v>
+        <v>1020001</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>layer-1</t>
+          <t>ordinary</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>120</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1007,14 +1007,14 @@
     </row>
     <row r="19">
       <c r="B19" t="n">
-        <v>109</v>
+        <v>1030001</v>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>layer-1</t>
+          <t>ordinary</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>120</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1038,14 +1038,14 @@
     </row>
     <row r="20">
       <c r="B20" t="n">
-        <v>110</v>
+        <v>1040001</v>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>layer-1</t>
+          <t>ordinary</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1069,14 +1069,14 @@
     </row>
     <row r="21">
       <c r="B21" t="n">
-        <v>111</v>
+        <v>1050001</v>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>layer-1</t>
+          <t>ordinary</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1100,14 +1100,14 @@
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>95</v>
+        <v>1060001</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>layer-1</t>
+          <t>ordinary</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>720</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1131,14 +1131,14 @@
     </row>
     <row r="23">
       <c r="B23" t="n">
-        <v>96</v>
+        <v>1070001</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>layer-1</t>
+          <t>ordinary</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>450</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1162,14 +1162,14 @@
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>97</v>
+        <v>1080001</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>layer-1</t>
+          <t>ordinary</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>360</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1193,14 +1193,14 @@
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>98</v>
+        <v>1090005</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>layer-1</t>
+          <t>ordinary</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1224,32 +1224,2295 @@
     </row>
     <row r="26">
       <c r="B26" t="n">
+        <v>1090006</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>1090008</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>1090010</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H28" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>96</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>1090002</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>1090003</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>1090011</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>1090009</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>1090012</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>1090004</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>95</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>1100002</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>1100011</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H38" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>1100004</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H39" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>100</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H40" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>1100007</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H41" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>1100010</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H42" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>1100003</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H43" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>1100006</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H44" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>97</v>
+      </c>
+      <c r="C45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H45" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>1100009</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H46" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>1100012</v>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H47" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="n">
         <v>99</v>
       </c>
-      <c r="C26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>layer-1</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Ordinary</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H26" t="b">
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H48" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>103</v>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H49" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="n">
+        <v>104</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H50" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>1110002</v>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="n">
+        <v>1110006</v>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H52" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="n">
+        <v>1110008</v>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H53" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>1110004</v>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H54" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>1110011</v>
+      </c>
+      <c r="C55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H55" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="n">
+        <v>1110003</v>
+      </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H56" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="n">
+        <v>102</v>
+      </c>
+      <c r="C57" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H57" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="n">
+        <v>1110009</v>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H58" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="n">
+        <v>1110001</v>
+      </c>
+      <c r="C59" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H59" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="n">
+        <v>1110005</v>
+      </c>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H60" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="n">
+        <v>1120007</v>
+      </c>
+      <c r="C61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H61" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="n">
+        <v>1120010</v>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H62" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="n">
+        <v>1120011</v>
+      </c>
+      <c r="C63" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H63" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="n">
+        <v>1120003</v>
+      </c>
+      <c r="C64" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H64" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="n">
+        <v>106</v>
+      </c>
+      <c r="C65" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H65" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="n">
+        <v>107</v>
+      </c>
+      <c r="C66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H66" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="n">
+        <v>1120001</v>
+      </c>
+      <c r="C67" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H67" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="n">
+        <v>1120004</v>
+      </c>
+      <c r="C68" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H68" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="n">
+        <v>1120012</v>
+      </c>
+      <c r="C69" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H69" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="n">
+        <v>108</v>
+      </c>
+      <c r="C70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H70" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="n">
+        <v>1120002</v>
+      </c>
+      <c r="C71" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H71" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="n">
+        <v>1120006</v>
+      </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H72" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="n">
+        <v>1130003</v>
+      </c>
+      <c r="C73" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H73" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="n">
+        <v>1130011</v>
+      </c>
+      <c r="C74" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H74" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="n">
+        <v>1130001</v>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H75" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="n">
+        <v>1130004</v>
+      </c>
+      <c r="C76" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H76" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="n">
+        <v>1130005</v>
+      </c>
+      <c r="C77" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H77" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="n">
+        <v>1130008</v>
+      </c>
+      <c r="C78" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H78" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="n">
+        <v>1130010</v>
+      </c>
+      <c r="C79" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H79" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="n">
+        <v>1130012</v>
+      </c>
+      <c r="C80" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H80" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="n">
+        <v>1130002</v>
+      </c>
+      <c r="C81" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H81" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="n">
+        <v>1130007</v>
+      </c>
+      <c r="C82" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H82" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="n">
+        <v>1130009</v>
+      </c>
+      <c r="C83" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H83" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="n">
+        <v>1130006</v>
+      </c>
+      <c r="C84" t="n">
+        <v>1</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H84" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="n">
+        <v>1140001</v>
+      </c>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H85" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="n">
+        <v>1140006</v>
+      </c>
+      <c r="C86" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H86" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="n">
+        <v>1140007</v>
+      </c>
+      <c r="C87" t="n">
+        <v>1</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H87" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="n">
+        <v>1140012</v>
+      </c>
+      <c r="C88" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H88" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="n">
+        <v>110</v>
+      </c>
+      <c r="C89" t="n">
+        <v>1</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H89" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="n">
+        <v>1140008</v>
+      </c>
+      <c r="C90" t="n">
+        <v>1</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H90" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="n">
+        <v>1140009</v>
+      </c>
+      <c r="C91" t="n">
+        <v>1</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H91" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="n">
+        <v>1140002</v>
+      </c>
+      <c r="C92" t="n">
+        <v>1</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H92" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="n">
+        <v>1140003</v>
+      </c>
+      <c r="C93" t="n">
+        <v>1</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H93" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="n">
+        <v>1140004</v>
+      </c>
+      <c r="C94" t="n">
+        <v>1</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H94" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="n">
+        <v>1140005</v>
+      </c>
+      <c r="C95" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H95" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="n">
+        <v>1140010</v>
+      </c>
+      <c r="C96" t="n">
+        <v>1</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H96" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="n">
+        <v>1150002</v>
+      </c>
+      <c r="C97" t="n">
+        <v>1</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H97" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="n">
+        <v>111</v>
+      </c>
+      <c r="C98" t="n">
+        <v>1</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H98" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="n">
+        <v>1150003</v>
+      </c>
+      <c r="C99" t="n">
+        <v>1</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>ordinary</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H99" t="b">
         <v>1</v>
       </c>
     </row>
